--- a/샘플_신청데이터_통합유형_1건.xlsx
+++ b/샘플_신청데이터_통합유형_1건.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="141">
   <si>
     <t>접수번호</t>
   </si>
@@ -42,118 +42,115 @@
     <t>이메일</t>
   </si>
   <si>
+    <t>제공형태</t>
+  </si>
+  <si>
+    <t>제품분류</t>
+  </si>
+  <si>
+    <t>개요</t>
+  </si>
+  <si>
+    <t>인공지능적용목적</t>
+  </si>
+  <si>
+    <t>인공지능적용범위</t>
+  </si>
+  <si>
+    <t>구조도파일명</t>
+  </si>
+  <si>
+    <t>명세서작성방식</t>
+  </si>
+  <si>
+    <t>명세서파일명</t>
+  </si>
+  <si>
+    <t>기타제출서류파일명</t>
+  </si>
+  <si>
+    <t>보유인증</t>
+  </si>
+  <si>
+    <t>인증서파일명</t>
+  </si>
+  <si>
+    <t>열람이용동의여부</t>
+  </si>
+  <si>
+    <t>개인정보수집이용동의여부</t>
+  </si>
+  <si>
+    <t>개인정보3자제공동의여부</t>
+  </si>
+  <si>
+    <t>특기사항</t>
+  </si>
+  <si>
+    <t>AI202600099</t>
+  </si>
+  <si>
+    <t>2026-07-09</t>
+  </si>
+  <si>
+    <t>주식회사 옴니헬스AI</t>
+  </si>
+  <si>
+    <t>345-67-89012</t>
+  </si>
+  <si>
+    <t>박대표</t>
+  </si>
+  <si>
+    <t>서울특별시 성동구 성수이로 20, 4층</t>
+  </si>
+  <si>
+    <t>정담당</t>
+  </si>
+  <si>
+    <t>02-3456-7890</t>
+  </si>
+  <si>
+    <t>pilot@omnihealth.example</t>
+  </si>
+  <si>
+    <t>SaaS(클라우드 서비스형)</t>
+  </si>
+  <si>
+    <t>서비스</t>
+  </si>
+  <si>
+    <t>흉부 CT 결절 탐지부터 판독 리포트 생성·번역, 현장 초음파 실시간 분석, 종합 대시보드까지 하나의 플랫폼에서 제공하는 AI 기반 통합 영상진단 지원 서비스입니다. 자체 학습 모델, 오픈소스 파인튜닝 모델, 외부 API, 온디바이스 추론, 혼합형 구성을 각 기능별로 적용해 5가지 AI 구현 방식을 모두 시연합니다.</t>
+  </si>
+  <si>
+    <t>판독 전 단계를 자동화·보조하여 판독 시간을 단축하고 초기 스크리닝 정확도와 접근성을 높이는 것을 목적으로 합니다.</t>
+  </si>
+  <si>
+    <t>CT/초음파 영상 업로드 또는 실시간 촬영 → 병변 탐지 → 판독 소견 생성 → 다국어 번역 → 현장 실시간 분석 → 종합 대시보드 표출 전 구간에 AI가 적용됩니다.</t>
+  </si>
+  <si>
+    <t>omnidx-architecture.png</t>
+  </si>
+  <si>
+    <t>직접제출</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>해당없음</t>
+  </si>
+  <si>
+    <t>동의</t>
+  </si>
+  <si>
+    <t>5개 AI 구현 방식(A~E)을 모두 포함하는 통합 샘플 — 유형별 증빙 예시 데모용</t>
+  </si>
+  <si>
+    <t>연번</t>
+  </si>
+  <si>
     <t>제품 또는 서비스 모델명</t>
-  </si>
-  <si>
-    <t>제공형태</t>
-  </si>
-  <si>
-    <t>제품분류</t>
-  </si>
-  <si>
-    <t>개요</t>
-  </si>
-  <si>
-    <t>인공지능적용목적</t>
-  </si>
-  <si>
-    <t>인공지능적용범위</t>
-  </si>
-  <si>
-    <t>구조도파일명</t>
-  </si>
-  <si>
-    <t>명세서작성방식</t>
-  </si>
-  <si>
-    <t>명세서파일명</t>
-  </si>
-  <si>
-    <t>기타제출서류파일명</t>
-  </si>
-  <si>
-    <t>보유인증</t>
-  </si>
-  <si>
-    <t>인증서파일명</t>
-  </si>
-  <si>
-    <t>열람이용동의여부</t>
-  </si>
-  <si>
-    <t>개인정보수집이용동의여부</t>
-  </si>
-  <si>
-    <t>개인정보3자제공동의여부</t>
-  </si>
-  <si>
-    <t>특기사항</t>
-  </si>
-  <si>
-    <t>AI202600099</t>
-  </si>
-  <si>
-    <t>2026-07-09</t>
-  </si>
-  <si>
-    <t>주식회사 옴니헬스AI</t>
-  </si>
-  <si>
-    <t>345-67-89012</t>
-  </si>
-  <si>
-    <t>박대표</t>
-  </si>
-  <si>
-    <t>서울특별시 성동구 성수이로 20, 4층</t>
-  </si>
-  <si>
-    <t>정담당</t>
-  </si>
-  <si>
-    <t>02-3456-7890</t>
-  </si>
-  <si>
-    <t>pilot@omnihealth.example</t>
-  </si>
-  <si>
-    <t>OmniDx 통합 영상판독 플랫폼</t>
-  </si>
-  <si>
-    <t>SaaS(클라우드 서비스형)</t>
-  </si>
-  <si>
-    <t>서비스</t>
-  </si>
-  <si>
-    <t>흉부 CT 결절 탐지부터 판독 리포트 생성·번역, 현장 초음파 실시간 분석, 종합 대시보드까지 하나의 플랫폼에서 제공하는 AI 기반 통합 영상진단 지원 서비스입니다. 자체 학습 모델, 오픈소스 파인튜닝 모델, 외부 API, 온디바이스 추론, 혼합형 구성을 각 기능별로 적용해 5가지 AI 구현 방식을 모두 시연합니다.</t>
-  </si>
-  <si>
-    <t>판독 전 단계를 자동화·보조하여 판독 시간을 단축하고 초기 스크리닝 정확도와 접근성을 높이는 것을 목적으로 합니다.</t>
-  </si>
-  <si>
-    <t>CT/초음파 영상 업로드 또는 실시간 촬영 → 병변 탐지 → 판독 소견 생성 → 다국어 번역 → 현장 실시간 분석 → 종합 대시보드 표출 전 구간에 AI가 적용됩니다.</t>
-  </si>
-  <si>
-    <t>omnidx-architecture.png</t>
-  </si>
-  <si>
-    <t>직접제출</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>해당없음</t>
-  </si>
-  <si>
-    <t>동의</t>
-  </si>
-  <si>
-    <t>5개 AI 구현 방식(A~E)을 모두 포함하는 통합 샘플 — 유형별 증빙 예시 데모용</t>
-  </si>
-  <si>
-    <t>연번</t>
   </si>
   <si>
     <t>세부품명번호</t>
@@ -828,7 +825,7 @@
   <dimension ref="A1:Y2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="25" width="22" customWidth="1"/>
+    <col min="1" max="24" width="22" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.25">
@@ -904,90 +901,84 @@
       <c r="X1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="1" t="s">
-        <v>24</v>
-      </c>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" t="s">
         <v>25</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>26</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>27</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>28</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>29</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>30</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>31</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>32</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>33</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>34</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>35</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>36</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>37</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>38</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>39</v>
       </c>
-      <c r="P2" t="s">
-        <v>40</v>
-      </c>
       <c r="Q2" t="s">
+        <v>40</v>
+      </c>
+      <c r="R2" t="s">
+        <v>40</v>
+      </c>
+      <c r="S2" t="s">
         <v>41</v>
       </c>
-      <c r="R2" t="s">
-        <v>42</v>
-      </c>
-      <c r="S2" t="s">
-        <v>42</v>
-      </c>
       <c r="T2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="U2" t="s">
         <v>42</v>
       </c>
       <c r="V2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="W2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="X2" t="s">
-        <v>44</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -1004,55 +995,55 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2" t="s">
         <v>49</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>50</v>
-      </c>
-      <c r="E2" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B3">
         <v>2</v>
       </c>
       <c r="C3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3" t="s">
         <v>52</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>53</v>
-      </c>
-      <c r="E3" t="s">
-        <v>54</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -1069,429 +1060,429 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>75</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D2" t="s">
         <v>77</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>78</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>79</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>80</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>81</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>82</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>83</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>84</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>85</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
+        <v>40</v>
+      </c>
+      <c r="N2" t="s">
+        <v>40</v>
+      </c>
+      <c r="O2" t="s">
+        <v>40</v>
+      </c>
+      <c r="P2" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>40</v>
+      </c>
+      <c r="R2" t="s">
+        <v>40</v>
+      </c>
+      <c r="S2" t="s">
+        <v>40</v>
+      </c>
+      <c r="T2" t="s">
+        <v>40</v>
+      </c>
+      <c r="U2" t="s">
         <v>86</v>
       </c>
-      <c r="M2" t="s">
-        <v>42</v>
-      </c>
-      <c r="N2" t="s">
-        <v>42</v>
-      </c>
-      <c r="O2" t="s">
-        <v>42</v>
-      </c>
-      <c r="P2" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>42</v>
-      </c>
-      <c r="R2" t="s">
-        <v>42</v>
-      </c>
-      <c r="S2" t="s">
-        <v>42</v>
-      </c>
-      <c r="T2" t="s">
-        <v>42</v>
-      </c>
-      <c r="U2" t="s">
+      <c r="V2" t="s">
         <v>87</v>
       </c>
-      <c r="V2" t="s">
+      <c r="W2" t="s">
         <v>88</v>
-      </c>
-      <c r="W2" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B3">
         <v>2</v>
       </c>
       <c r="C3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D3" t="s">
         <v>90</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>91</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>92</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>93</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>94</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>95</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>96</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
+        <v>40</v>
+      </c>
+      <c r="L3" t="s">
+        <v>40</v>
+      </c>
+      <c r="M3" t="s">
         <v>97</v>
       </c>
-      <c r="K3" t="s">
-        <v>42</v>
-      </c>
-      <c r="L3" t="s">
-        <v>42</v>
-      </c>
-      <c r="M3" t="s">
+      <c r="N3" t="s">
         <v>98</v>
       </c>
-      <c r="N3" t="s">
+      <c r="O3" t="s">
         <v>99</v>
       </c>
-      <c r="O3" t="s">
+      <c r="P3" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>40</v>
+      </c>
+      <c r="R3" t="s">
+        <v>40</v>
+      </c>
+      <c r="S3" t="s">
+        <v>40</v>
+      </c>
+      <c r="T3" t="s">
+        <v>40</v>
+      </c>
+      <c r="U3" t="s">
         <v>100</v>
       </c>
-      <c r="P3" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>42</v>
-      </c>
-      <c r="R3" t="s">
-        <v>42</v>
-      </c>
-      <c r="S3" t="s">
-        <v>42</v>
-      </c>
-      <c r="T3" t="s">
-        <v>42</v>
-      </c>
-      <c r="U3" t="s">
+      <c r="V3" t="s">
         <v>101</v>
       </c>
-      <c r="V3" t="s">
+      <c r="W3" t="s">
         <v>102</v>
-      </c>
-      <c r="W3" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B4">
         <v>3</v>
       </c>
       <c r="C4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D4" t="s">
         <v>104</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>105</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>106</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>107</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>108</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>109</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>110</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
+        <v>40</v>
+      </c>
+      <c r="L4" t="s">
+        <v>40</v>
+      </c>
+      <c r="M4" t="s">
+        <v>40</v>
+      </c>
+      <c r="N4" t="s">
+        <v>40</v>
+      </c>
+      <c r="O4" t="s">
+        <v>40</v>
+      </c>
+      <c r="P4" t="s">
         <v>111</v>
       </c>
-      <c r="K4" t="s">
-        <v>42</v>
-      </c>
-      <c r="L4" t="s">
-        <v>42</v>
-      </c>
-      <c r="M4" t="s">
-        <v>42</v>
-      </c>
-      <c r="N4" t="s">
-        <v>42</v>
-      </c>
-      <c r="O4" t="s">
-        <v>42</v>
-      </c>
-      <c r="P4" t="s">
+      <c r="Q4" t="s">
+        <v>40</v>
+      </c>
+      <c r="R4" t="s">
+        <v>40</v>
+      </c>
+      <c r="S4" t="s">
+        <v>40</v>
+      </c>
+      <c r="T4" t="s">
+        <v>40</v>
+      </c>
+      <c r="U4" t="s">
         <v>112</v>
       </c>
-      <c r="Q4" t="s">
-        <v>42</v>
-      </c>
-      <c r="R4" t="s">
-        <v>42</v>
-      </c>
-      <c r="S4" t="s">
-        <v>42</v>
-      </c>
-      <c r="T4" t="s">
-        <v>42</v>
-      </c>
-      <c r="U4" t="s">
+      <c r="V4" t="s">
         <v>113</v>
       </c>
-      <c r="V4" t="s">
+      <c r="W4" t="s">
         <v>114</v>
-      </c>
-      <c r="W4" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B5">
         <v>4</v>
       </c>
       <c r="C5" t="s">
+        <v>115</v>
+      </c>
+      <c r="D5" t="s">
         <v>116</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>117</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>118</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>119</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>120</v>
       </c>
-      <c r="H5" t="s">
+      <c r="I5" t="s">
         <v>121</v>
       </c>
-      <c r="I5" t="s">
+      <c r="J5" t="s">
         <v>122</v>
       </c>
-      <c r="J5" t="s">
+      <c r="K5" t="s">
+        <v>40</v>
+      </c>
+      <c r="L5" t="s">
+        <v>40</v>
+      </c>
+      <c r="M5" t="s">
+        <v>40</v>
+      </c>
+      <c r="N5" t="s">
+        <v>40</v>
+      </c>
+      <c r="O5" t="s">
+        <v>40</v>
+      </c>
+      <c r="P5" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q5" t="s">
         <v>123</v>
       </c>
-      <c r="K5" t="s">
-        <v>42</v>
-      </c>
-      <c r="L5" t="s">
-        <v>42</v>
-      </c>
-      <c r="M5" t="s">
-        <v>42</v>
-      </c>
-      <c r="N5" t="s">
-        <v>42</v>
-      </c>
-      <c r="O5" t="s">
-        <v>42</v>
-      </c>
-      <c r="P5" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q5" t="s">
+      <c r="R5" t="s">
         <v>124</v>
       </c>
-      <c r="R5" t="s">
+      <c r="S5" t="s">
+        <v>40</v>
+      </c>
+      <c r="T5" t="s">
+        <v>40</v>
+      </c>
+      <c r="U5" t="s">
         <v>125</v>
       </c>
-      <c r="S5" t="s">
-        <v>42</v>
-      </c>
-      <c r="T5" t="s">
-        <v>42</v>
-      </c>
-      <c r="U5" t="s">
+      <c r="V5" t="s">
         <v>126</v>
       </c>
-      <c r="V5" t="s">
+      <c r="W5" t="s">
         <v>127</v>
-      </c>
-      <c r="W5" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B6">
         <v>5</v>
       </c>
       <c r="C6" t="s">
+        <v>128</v>
+      </c>
+      <c r="D6" t="s">
         <v>129</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>130</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>131</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>132</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
         <v>133</v>
       </c>
-      <c r="H6" t="s">
+      <c r="I6" t="s">
         <v>134</v>
       </c>
-      <c r="I6" t="s">
+      <c r="J6" t="s">
         <v>135</v>
       </c>
-      <c r="J6" t="s">
+      <c r="K6" t="s">
+        <v>40</v>
+      </c>
+      <c r="L6" t="s">
+        <v>40</v>
+      </c>
+      <c r="M6" t="s">
+        <v>40</v>
+      </c>
+      <c r="N6" t="s">
+        <v>40</v>
+      </c>
+      <c r="O6" t="s">
+        <v>40</v>
+      </c>
+      <c r="P6" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>40</v>
+      </c>
+      <c r="R6" t="s">
+        <v>40</v>
+      </c>
+      <c r="S6" t="s">
         <v>136</v>
       </c>
-      <c r="K6" t="s">
-        <v>42</v>
-      </c>
-      <c r="L6" t="s">
-        <v>42</v>
-      </c>
-      <c r="M6" t="s">
-        <v>42</v>
-      </c>
-      <c r="N6" t="s">
-        <v>42</v>
-      </c>
-      <c r="O6" t="s">
-        <v>42</v>
-      </c>
-      <c r="P6" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>42</v>
-      </c>
-      <c r="R6" t="s">
-        <v>42</v>
-      </c>
-      <c r="S6" t="s">
+      <c r="T6" t="s">
         <v>137</v>
       </c>
-      <c r="T6" t="s">
+      <c r="U6" t="s">
         <v>138</v>
       </c>
-      <c r="U6" t="s">
+      <c r="V6" t="s">
         <v>139</v>
       </c>
-      <c r="V6" t="s">
+      <c r="W6" t="s">
         <v>140</v>
-      </c>
-      <c r="W6" t="s">
-        <v>141</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>